--- a/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-22T09:03:21+00:00</t>
+    <t>2024-07-22T10:03:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-22T10:03:18+00:00</t>
+    <t>2024-07-22T11:36:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-22T11:36:24+00:00</t>
+    <t>2024-07-24T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T13:54:21+00:00</t>
+    <t>2024-07-24T14:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T14:54:06+00:00</t>
+    <t>2024-07-24T15:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/Eric-fonctionnel-schema-evaluation/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T15:26:16+00:00</t>
+    <t>2024-07-24T15:54:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
